--- a/企業（きぎょう）.xlsx
+++ b/企業（きぎょう）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="19716" windowHeight="9708"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="179">
   <si>
     <t>面接</t>
   </si>
@@ -407,7 +407,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
+        <charset val="128"/>
       </rPr>
       <t>离职）</t>
     </r>
@@ -446,6 +446,30 @@
     <t>ほうしゅう</t>
   </si>
   <si>
+    <t>辞退</t>
+  </si>
+  <si>
+    <t>じたい</t>
+  </si>
+  <si>
+    <t>（礼貌拒绝）</t>
+  </si>
+  <si>
+    <t>発送</t>
+  </si>
+  <si>
+    <t>はっそう</t>
+  </si>
+  <si>
+    <t>（发送）</t>
+  </si>
+  <si>
+    <t>報酬額</t>
+  </si>
+  <si>
+    <t>ほうしゅうが</t>
+  </si>
+  <si>
     <t>仕事</t>
   </si>
   <si>
@@ -455,19 +479,16 @@
     <t>試合</t>
   </si>
   <si>
-    <t>発送</t>
-  </si>
-  <si>
-    <t>はっそう</t>
-  </si>
-  <si>
-    <t>（发送）</t>
-  </si>
-  <si>
-    <t>報酬額</t>
-  </si>
-  <si>
-    <t>ほうしゅうが</t>
+    <t>担当</t>
+  </si>
+  <si>
+    <t>たんとう</t>
+  </si>
+  <si>
+    <t>通勤</t>
+  </si>
+  <si>
+    <t>つうきん</t>
   </si>
   <si>
     <t>終身</t>
@@ -476,43 +497,25 @@
     <t>しゅうしん</t>
   </si>
   <si>
-    <t>担当</t>
-  </si>
-  <si>
-    <t>たんとう</t>
-  </si>
-  <si>
-    <t>通勤</t>
-  </si>
-  <si>
-    <t>つうきん</t>
+    <t>方針</t>
+  </si>
+  <si>
+    <t>ほうしん</t>
+  </si>
+  <si>
+    <t>月給</t>
+  </si>
+  <si>
+    <t>げっきゅう</t>
+  </si>
+  <si>
+    <t>（月薪）</t>
   </si>
   <si>
     <t>雇用</t>
   </si>
   <si>
     <t>こよう</t>
-  </si>
-  <si>
-    <t>方針</t>
-  </si>
-  <si>
-    <t>ほうしん</t>
-  </si>
-  <si>
-    <t>月給</t>
-  </si>
-  <si>
-    <t>げっきゅう</t>
-  </si>
-  <si>
-    <t>（月薪）</t>
-  </si>
-  <si>
-    <t>新卒</t>
-  </si>
-  <si>
-    <t>しんそつ</t>
   </si>
   <si>
     <t>人手</t>
@@ -545,6 +548,12 @@
     <t>人手不足｜ひとでぶそく</t>
   </si>
   <si>
+    <t>新卒</t>
+  </si>
+  <si>
+    <t>しんそつ</t>
+  </si>
+  <si>
     <t>中途</t>
   </si>
   <si>
@@ -665,6 +674,15 @@
     <t>（女社员因结婚而离职）</t>
   </si>
   <si>
+    <t>常勤</t>
+  </si>
+  <si>
+    <t>じょうきん</t>
+  </si>
+  <si>
+    <t>（经常上班，专职）</t>
+  </si>
+  <si>
     <t>案件</t>
   </si>
   <si>
@@ -705,7 +723,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -730,13 +748,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -893,7 +904,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1199,148 +1210,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1668,7 +1679,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:M34"/>
+  <dimension ref="A2:M36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="9.55555555555556" customWidth="1"/>
@@ -2026,13 +2037,13 @@
       </c>
     </row>
     <row r="16" ht="18" spans="1:13">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>102</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>104</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -2058,86 +2069,86 @@
       <c r="B17" s="1" t="s">
         <v>111</v>
       </c>
+      <c r="C17" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="E17" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:11">
       <c r="A19" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C22" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2148,23 +2159,23 @@
       <c r="B23" s="1" t="s">
         <v>137</v>
       </c>
+      <c r="C23" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="24" ht="18" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C25" s="3" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2175,31 +2186,31 @@
       <c r="B26" s="1" t="s">
         <v>144</v>
       </c>
+      <c r="C26" s="3" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="27" ht="18" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:11">
       <c r="A29" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C29" t="s">
         <v>151</v>
       </c>
     </row>
@@ -2210,40 +2221,62 @@
       <c r="B30" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="C30" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="31" ht="18" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:11">
       <c r="A32" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C34" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="35" ht="18" spans="1:3">
+      <c r="A35" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C35" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>166</v>
+      </c>
+      <c r="B36" t="s">
+        <v>167</v>
+      </c>
+      <c r="C36" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2263,42 +2296,42 @@
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:2">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:2">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:2">
       <c r="A6" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/企業（きぎょう）.xlsx
+++ b/企業（きぎょう）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19716" windowHeight="9708"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="183">
   <si>
     <t>面接</t>
   </si>
@@ -518,6 +518,12 @@
     <t>こよう</t>
   </si>
   <si>
+    <t>中間考査</t>
+  </si>
+  <si>
+    <t>ちゅうかんこうさ</t>
+  </si>
+  <si>
     <t>人手</t>
   </si>
   <si>
@@ -554,6 +560,12 @@
     <t>しんそつ</t>
   </si>
   <si>
+    <t>中間報告</t>
+  </si>
+  <si>
+    <t>ちゅうかんほうこく</t>
+  </si>
+  <si>
     <t>中途</t>
   </si>
   <si>
@@ -897,14 +909,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2115,168 +2127,180 @@
       <c r="B19" s="1" t="s">
         <v>125</v>
       </c>
+      <c r="E19" t="s">
+        <v>126</v>
+      </c>
+      <c r="F19" t="s">
+        <v>127</v>
+      </c>
       <c r="H19" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
+      </c>
+      <c r="E20" t="s">
+        <v>134</v>
+      </c>
+      <c r="F20" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:11">
       <c r="A23" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C23" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:11">
       <c r="A29" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C30" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:11">
       <c r="A32" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C35" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C36" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2296,42 +2320,42 @@
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:2">
       <c r="A3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:2">
       <c r="A4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:2">
       <c r="A6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/企業（きぎょう）.xlsx
+++ b/企業（きぎょう）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="185">
   <si>
     <t>面接</t>
   </si>
@@ -693,6 +693,12 @@
   </si>
   <si>
     <t>（经常上班，专职）</t>
+  </si>
+  <si>
+    <t>功績</t>
+  </si>
+  <si>
+    <t>こうせき</t>
   </si>
   <si>
     <t>案件</t>
@@ -1691,7 +1697,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:M36"/>
+  <dimension ref="A2:M37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="9.55555555555556" customWidth="1"/>
@@ -2301,6 +2307,14 @@
       </c>
       <c r="C36" t="s">
         <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>173</v>
+      </c>
+      <c r="B37" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2320,42 +2334,42 @@
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:2">
       <c r="A3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:2">
       <c r="A4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:2">
       <c r="A6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/企業（きぎょう）.xlsx
+++ b/企業（きぎょう）.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="189">
   <si>
     <t>面接</t>
   </si>
@@ -531,12 +531,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <charset val="128"/>
-      </rPr>
       <t>（</t>
     </r>
     <r>
@@ -544,14 +538,14 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <charset val="134"/>
+        <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
       <t>人力，人手）</t>
     </r>
   </si>
   <si>
-    <t>人手不足｜ひとでぶそく</t>
+    <t>ひとでぶそく|人手不足</t>
   </si>
   <si>
     <t>新卒</t>
@@ -570,6 +564,18 @@
   </si>
   <si>
     <t>ちゅうと</t>
+  </si>
+  <si>
+    <t>昇進</t>
+  </si>
+  <si>
+    <t>しょうしん</t>
+  </si>
+  <si>
+    <t>（晋级，升职）</t>
+  </si>
+  <si>
+    <t>部長に昇進する｜晋升为部长</t>
   </si>
   <si>
     <t>初心者</t>
@@ -915,14 +921,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1697,17 +1703,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:M37"/>
+  <dimension ref="A2:N37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="9.55555555555556" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="27.1111111111111" customWidth="1"/>
     <col min="5" max="5" width="16.1111111111111" customWidth="1"/>
-    <col min="9" max="9" width="13.8888888888889" customWidth="1"/>
+    <col min="10" max="10" width="13.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="18" spans="1:13">
+    <row r="2" ht="18" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1723,20 +1729,20 @@
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="18" spans="1:13">
+    <row r="3" ht="18" spans="1:14">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1749,20 +1755,20 @@
       <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="18" spans="1:13">
+    <row r="4" ht="18" spans="1:14">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -1775,23 +1781,23 @@
       <c r="F4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="18" spans="1:13">
+    <row r="5" ht="18" spans="1:14">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
@@ -1804,23 +1810,23 @@
       <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>30</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>31</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" ht="18" spans="1:13">
+    <row r="6" ht="18" spans="1:14">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
@@ -1833,14 +1839,14 @@
       <c r="F6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" ht="18" spans="1:13">
+    <row r="7" ht="18" spans="1:14">
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
@@ -1857,14 +1863,14 @@
       <c r="F7" t="s">
         <v>43</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>44</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" ht="18" spans="1:13">
+    <row r="8" ht="18" spans="1:14">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -1880,14 +1886,14 @@
       <c r="F8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" ht="18" spans="1:13">
+    <row r="9" ht="18" spans="1:14">
       <c r="A9" s="1" t="s">
         <v>53</v>
       </c>
@@ -1900,14 +1906,14 @@
       <c r="F9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="10" ht="18" spans="1:13">
+    <row r="10" ht="18" spans="1:14">
       <c r="A10" t="s">
         <v>59</v>
       </c>
@@ -1920,14 +1926,14 @@
       <c r="F10" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" ht="18" spans="1:13">
+    <row r="11" ht="18" spans="1:14">
       <c r="A11" t="s">
         <v>65</v>
       </c>
@@ -1943,14 +1949,14 @@
       <c r="F11" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="12" ht="18" spans="1:13">
+    <row r="12" ht="18" spans="1:14">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -1966,17 +1972,17 @@
       <c r="F12" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="13" ht="18" spans="1:13">
+    <row r="13" ht="18" spans="1:14">
       <c r="A13" t="s">
         <v>80</v>
       </c>
@@ -1992,17 +1998,17 @@
       <c r="F13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" ht="18" spans="1:13">
+    <row r="14" ht="18" spans="1:14">
       <c r="A14" s="1" t="s">
         <v>88</v>
       </c>
@@ -2018,17 +2024,17 @@
       <c r="F14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="15" ht="18" spans="1:13">
+    <row r="15" ht="18" spans="1:14">
       <c r="A15" s="1" t="s">
         <v>95</v>
       </c>
@@ -2047,14 +2053,14 @@
       <c r="G15" t="s">
         <v>99</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="16" ht="18" spans="1:13">
+    <row r="16" ht="18" spans="1:14">
       <c r="A16" t="s">
         <v>102</v>
       </c>
@@ -2073,14 +2079,14 @@
       <c r="G16" t="s">
         <v>107</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="17" ht="18" spans="1:11">
+    <row r="17" ht="18" spans="1:12">
       <c r="A17" s="1" t="s">
         <v>110</v>
       </c>
@@ -2096,14 +2102,14 @@
       <c r="F17" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="18" ht="18" spans="1:11">
+    <row r="18" ht="18" spans="1:12">
       <c r="A18" s="1" t="s">
         <v>117</v>
       </c>
@@ -2116,17 +2122,17 @@
       <c r="F18" t="s">
         <v>120</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="19" ht="18" spans="1:11">
+    <row r="19" ht="18" spans="1:12">
       <c r="A19" s="1" t="s">
         <v>124</v>
       </c>
@@ -2139,20 +2145,20 @@
       <c r="F19" t="s">
         <v>127</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="20" ht="18" spans="1:11">
+    <row r="20" ht="18" spans="1:12">
       <c r="A20" s="1" t="s">
         <v>132</v>
       </c>
@@ -2166,155 +2172,167 @@
         <v>135</v>
       </c>
     </row>
-    <row r="21" ht="18" spans="1:11">
+    <row r="21" ht="18" spans="1:12">
       <c r="A21" s="1" t="s">
         <v>136</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="22" ht="18" spans="1:11">
+      <c r="E21" t="s">
+        <v>138</v>
+      </c>
+      <c r="F21" t="s">
+        <v>139</v>
+      </c>
+      <c r="G21" t="s">
+        <v>140</v>
+      </c>
+      <c r="H21" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" ht="18" spans="1:12">
       <c r="A22" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="23" ht="18" spans="1:11">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" ht="18" spans="1:12">
       <c r="A23" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C23" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="24" ht="18" spans="1:11">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" ht="18" spans="1:12">
       <c r="A24" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="25" ht="18" spans="1:11">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" ht="18" spans="1:12">
       <c r="A25" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="26" ht="18" spans="1:11">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" ht="18" spans="1:12">
       <c r="A26" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="27" ht="18" spans="1:11">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" ht="18" spans="1:12">
       <c r="A27" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="28" ht="18" spans="1:11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="28" ht="18" spans="1:12">
       <c r="A28" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="29" ht="18" spans="1:11">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="29" ht="18" spans="1:12">
       <c r="A29" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="30" ht="18" spans="1:11">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" ht="18" spans="1:12">
       <c r="A30" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C30" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="31" ht="18" spans="1:11">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" ht="18" spans="1:12">
       <c r="A31" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="32" ht="18" spans="1:11">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" ht="18" spans="1:12">
       <c r="A32" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" ht="18" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C35" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C36" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B37" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2334,42 +2352,42 @@
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:2">
       <c r="A3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:2">
       <c r="A4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:2">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
